--- a/public/assets/templates/grad-engineering-oral-checklist.xlsx
+++ b/public/assets/templates/grad-engineering-oral-checklist.xlsx
@@ -698,14 +698,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>完整說明　https://tbd-web.vercel.app/pages/resources/engineering-graduate-oral.html</t>
+          <t>完整說明　https://tbd-edu.com/pages/resources/engineering-graduate-oral.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>TBD Studio ｜ https://tbd-web.vercel.app/pages/resources/tools.html</t>
+          <t>TBD Studio ｜ https://tbd-edu.com/pages/resources/tools.html</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>完整說明　https://tbd-web.vercel.app/pages/resources/engineering-graduate-oral.html</t>
+          <t>完整說明　https://tbd-edu.com/pages/resources/engineering-graduate-oral.html</t>
         </is>
       </c>
     </row>
